--- a/docs/collections/50nenshi/metadata/data.xlsx
+++ b/docs/collections/50nenshi/metadata/data.xlsx
@@ -44686,7 +44686,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>司法省法学校入学関係〔書類〕  明治九年</t>
+          <t>理科会粋 第四帙 東京近傍地質編</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
